--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -39,96 +39,96 @@
     <t xml:space="preserve">Villarrica</t>
   </si>
   <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilcún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitrufquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pucón</t>
   </si>
   <si>
-    <t xml:space="preserve">Vilcún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Loncoche</t>
   </si>
   <si>
+    <t xml:space="preserve">Teodoro Schmidt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lautaro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Galvarino</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freire</t>
+    <t xml:space="preserve">Collipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacautín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaico</t>
   </si>
   <si>
     <t xml:space="preserve">Cholchol</t>
   </si>
   <si>
-    <t xml:space="preserve">Lautaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teodoro Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaico</t>
+    <t xml:space="preserve">Carahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Imperial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traiguén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perquenco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saavedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
   </si>
   <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
-    <t xml:space="preserve">Curacautín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Imperial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saavedra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perquenco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipeuco</t>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curarrehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
     <t xml:space="preserve">Lonquimay</t>
   </si>
   <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curarrehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiguén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
-    <t xml:space="preserve">Angol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7251</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="3">
@@ -582,13 +582,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9115</v>
+        <v>9112</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4362</v>
+        <v>933</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3450</v>
+        <v>824</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2183</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9109</v>
+        <v>9105</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2151</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -650,13 +650,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9106</v>
+        <v>9115</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1930</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8">
@@ -667,13 +667,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>9112</v>
+        <v>9109</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1883</v>
+        <v>712</v>
       </c>
     </row>
     <row r="9">
@@ -684,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9105</v>
+        <v>9117</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1742</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10">
@@ -701,13 +701,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9121</v>
+        <v>9108</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1726</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11">
@@ -718,13 +718,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>9108</v>
+        <v>9106</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1617</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12">
@@ -735,13 +735,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9117</v>
+        <v>9202</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1574</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13">
@@ -752,13 +752,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9209</v>
+        <v>9203</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1526</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14">
@@ -769,13 +769,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9103</v>
+        <v>9209</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9203</v>
+        <v>9121</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
@@ -803,13 +803,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9111</v>
+        <v>9102</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1158</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17">
@@ -820,13 +820,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9116</v>
+        <v>9111</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>975</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18">
@@ -837,13 +837,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9202</v>
+        <v>9208</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>705</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19">
@@ -854,13 +854,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9208</v>
+        <v>9210</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>705</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20">
@@ -871,13 +871,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>9102</v>
+        <v>9113</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>693</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21">
@@ -888,13 +888,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9113</v>
+        <v>9116</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>577</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22">
@@ -905,13 +905,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9110</v>
+        <v>9211</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>575</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
@@ -922,13 +922,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9205</v>
+        <v>9110</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>557</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24">
@@ -939,13 +939,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9118</v>
+        <v>9103</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>553</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
@@ -956,13 +956,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9104</v>
+        <v>9118</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>415</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
@@ -973,13 +973,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>9210</v>
+        <v>9104</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>293</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
@@ -990,13 +990,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>9206</v>
+        <v>9201</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>226</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -1007,13 +1007,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>9207</v>
+        <v>9206</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>186</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
@@ -1024,13 +1024,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>9211</v>
+        <v>9207</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>116</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
@@ -1041,13 +1041,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9204</v>
+        <v>9205</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -1058,13 +1058,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>9107</v>
+        <v>9204</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-312</v>
+        <v>-169</v>
       </c>
     </row>
     <row r="32">
@@ -1075,13 +1075,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>9201</v>
+        <v>9107</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-695</v>
+        <v>-543</v>
       </c>
     </row>
     <row r="33">
@@ -1098,7 +1098,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-1736</v>
+        <v>-1662</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:19</t>
+    <t xml:space="preserve">2026-10-05 08:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
